--- a/artfynd/A 40414-2025 artfynd.xlsx
+++ b/artfynd/A 40414-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -887,6 +887,205 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128793087</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lillån, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>762371</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7167623</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128793085</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lillån, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>762262</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7167660</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack bild</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40414-2025 artfynd.xlsx
+++ b/artfynd/A 40414-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>128793087</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128793085</v>
       </c>
       <c r="B5" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40414-2025 artfynd.xlsx
+++ b/artfynd/A 40414-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>128793087</v>
       </c>
       <c r="B4" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40414-2025 artfynd.xlsx
+++ b/artfynd/A 40414-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>128793087</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128793085</v>
       </c>
       <c r="B5" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40414-2025 artfynd.xlsx
+++ b/artfynd/A 40414-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>128793087</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128793085</v>
       </c>
       <c r="B5" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40414-2025 artfynd.xlsx
+++ b/artfynd/A 40414-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>128793087</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40414-2025 artfynd.xlsx
+++ b/artfynd/A 40414-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>128793087</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128793085</v>
       </c>
       <c r="B5" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40414-2025 artfynd.xlsx
+++ b/artfynd/A 40414-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>128793087</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128793085</v>
       </c>
       <c r="B5" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40414-2025 artfynd.xlsx
+++ b/artfynd/A 40414-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113701716</v>
+        <v>113701705</v>
       </c>
       <c r="B2" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>762491</v>
+        <v>762390</v>
       </c>
       <c r="R2" t="n">
-        <v>7167661</v>
+        <v>7167600</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113701706</v>
+        <v>113701704</v>
       </c>
       <c r="B3" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>762375</v>
+        <v>762398</v>
       </c>
       <c r="R3" t="n">
-        <v>7167613</v>
+        <v>7167598</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128793087</v>
+        <v>113701706</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>762371</v>
+        <v>762375</v>
       </c>
       <c r="R4" t="n">
-        <v>7167623</v>
+        <v>7167613</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,12 +944,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128793085</v>
+        <v>113701716</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>762262</v>
+        <v>762491</v>
       </c>
       <c r="R5" t="n">
-        <v>7167660</v>
+        <v>7167661</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,17 +1046,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska ringhack bild</t>
+          <t>SWECO Naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,15 +1071,714 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>113701667</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lillån, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>762428</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7167593</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>113701707</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lillån, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>762335</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7167605</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>113701715</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lillån, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>762445</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7167599</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128793087</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lillån, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>762371</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7167623</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128793088</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lillån, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>762341</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7167605</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128793089</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lillån, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>762280</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7167623</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128793085</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lillån, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>762262</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7167660</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack bild</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40414-2025 artfynd.xlsx
+++ b/artfynd/A 40414-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113701705</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113701704</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113701706</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113701716</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113701667</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113701707</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113701715</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1483,6 +1523,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128793087</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1580,6 +1625,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128793088</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1677,6 +1727,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128793089</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1779,8 +1834,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128793085</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 40414-2025 artfynd.xlsx
+++ b/artfynd/A 40414-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113701705</v>
+        <v>136441169</v>
       </c>
       <c r="B2" t="n">
-        <v>91909</v>
+        <v>57993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillån, Vb</t>
+          <t>Hällfors, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>762390</v>
+        <v>762118</v>
       </c>
       <c r="R2" t="n">
-        <v>7167600</v>
+        <v>7167703</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,24 +753,24 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>SWECO Naturvärdesinventering</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -770,27 +778,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113701705</t>
+          <t>https://artportalen.se/Sighting/136441169</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113701704</v>
+        <v>113701705</v>
       </c>
       <c r="B3" t="n">
-        <v>83173</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>762398</v>
+        <v>762390</v>
       </c>
       <c r="R3" t="n">
-        <v>7167598</v>
+        <v>7167600</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,13 +896,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113701704</t>
+          <t>https://artportalen.se/Sighting/113701705</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113701706</v>
+        <v>113701704</v>
       </c>
       <c r="B4" t="n">
         <v>83173</v>
@@ -929,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>762375</v>
+        <v>762398</v>
       </c>
       <c r="R4" t="n">
-        <v>7167613</v>
+        <v>7167598</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,16 +1003,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113701706</t>
+          <t>https://artportalen.se/Sighting/113701704</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113701716</v>
+        <v>113701706</v>
       </c>
       <c r="B5" t="n">
-        <v>91930</v>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,21 +1020,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>762491</v>
+        <v>762375</v>
       </c>
       <c r="R5" t="n">
-        <v>7167661</v>
+        <v>7167613</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,38 +1110,38 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113701716</t>
+          <t>https://artportalen.se/Sighting/113701706</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113701667</v>
+        <v>113701716</v>
       </c>
       <c r="B6" t="n">
-        <v>79327</v>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>762428</v>
+        <v>762491</v>
       </c>
       <c r="R6" t="n">
-        <v>7167593</v>
+        <v>7167661</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,51 +1217,54 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113701667</t>
+          <t>https://artportalen.se/Sighting/113701716</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113701707</v>
+        <v>136439209</v>
       </c>
       <c r="B7" t="n">
-        <v>79327</v>
+        <v>92109</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lillån, Vb</t>
+          <t>Hällfors, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>762335</v>
+        <v>762353</v>
       </c>
       <c r="R7" t="n">
-        <v>7167605</v>
+        <v>7167636</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,17 +1291,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>SWECO Naturvärdesinventering</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1299,30 +1305,31 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113701707</t>
+          <t>https://artportalen.se/Sighting/136439209</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113701715</v>
+        <v>113701667</v>
       </c>
       <c r="B8" t="n">
         <v>79327</v>
@@ -1357,10 +1364,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>762445</v>
+        <v>762428</v>
       </c>
       <c r="R8" t="n">
-        <v>7167599</v>
+        <v>7167593</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,13 +1430,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113701715</t>
+          <t>https://artportalen.se/Sighting/113701667</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128793087</v>
+        <v>113701707</v>
       </c>
       <c r="B9" t="n">
         <v>79327</v>
@@ -1464,10 +1471,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>762371</v>
+        <v>762335</v>
       </c>
       <c r="R9" t="n">
-        <v>7167623</v>
+        <v>7167605</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,12 +1501,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1514,24 +1526,24 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128793087</t>
+          <t>https://artportalen.se/Sighting/113701707</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128793088</v>
+        <v>113701715</v>
       </c>
       <c r="B10" t="n">
         <v>79327</v>
@@ -1566,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>762341</v>
+        <v>762445</v>
       </c>
       <c r="R10" t="n">
-        <v>7167605</v>
+        <v>7167599</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,12 +1608,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1616,24 +1633,24 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128793088</t>
+          <t>https://artportalen.se/Sighting/113701715</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128793089</v>
+        <v>128793087</v>
       </c>
       <c r="B11" t="n">
         <v>79327</v>
@@ -1668,7 +1685,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>762280</v>
+        <v>762371</v>
       </c>
       <c r="R11" t="n">
         <v>7167623</v>
@@ -1729,38 +1746,38 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128793089</t>
+          <t>https://artportalen.se/Sighting/128793087</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128793085</v>
+        <v>128793088</v>
       </c>
       <c r="B12" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1787,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>762262</v>
+        <v>762341</v>
       </c>
       <c r="R12" t="n">
-        <v>7167660</v>
+        <v>7167605</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1808,11 +1825,6 @@
           <t>2025-09-23</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack bild</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1836,7 +1848,1011 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/128793088</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128793089</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lillån, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>762280</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7167623</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128793089</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136439863</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79460</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hällfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>762364</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7167600</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136439863</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136440087</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79460</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hällfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>762369</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7167609</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136440087</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136441073</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57990</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hällfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>762431</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7167685</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>bohål i 300+ år gammal tall med brandljud</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136441073</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128793085</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lillån, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>762262</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7167660</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack bild</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/128793085</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136440929</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57993</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hällfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>762486</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7167604</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136440929</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136440948</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57993</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hällfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>762506</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7167621</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136440948</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136440959</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57993</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hällfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>762515</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7167661</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136440959</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136441276</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57993</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hällfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>762263</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7167656</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136441276</t>
         </is>
       </c>
     </row>
@@ -1853,6 +2869,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40414-2025 artfynd.xlsx
+++ b/artfynd/A 40414-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136441169</v>
       </c>
       <c r="B2" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>136439209</v>
       </c>
       <c r="B7" t="n">
-        <v>92109</v>
+        <v>92122</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>136439863</v>
       </c>
       <c r="B14" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>136440087</v>
       </c>
       <c r="B15" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>136441073</v>
       </c>
       <c r="B16" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>136440929</v>
       </c>
       <c r="B18" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>136440948</v>
       </c>
       <c r="B19" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136440959</v>
       </c>
       <c r="B20" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>136441276</v>
       </c>
       <c r="B21" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 40414-2025 artfynd.xlsx
+++ b/artfynd/A 40414-2025 artfynd.xlsx
@@ -1226,7 +1226,7 @@
         <v>136439209</v>
       </c>
       <c r="B7" t="n">
-        <v>92122</v>
+        <v>92123</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>136439863</v>
       </c>
       <c r="B14" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>136440087</v>
       </c>
       <c r="B15" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
